--- a/file/table/DAPC_WindSpeedDirectionSample.xlsx
+++ b/file/table/DAPC_WindSpeedDirectionSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30618"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FEA018-2E37-4173-BCF5-2F6B4A0E2D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF24214-73D3-4B64-95B1-80ECAE919716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{72E4CBD1-0E4B-4C3C-BF1D-B2D91BD85BCD}"/>
+    <workbookView xWindow="-28882" yWindow="6465" windowWidth="14565" windowHeight="15563" xr2:uid="{72E4CBD1-0E4B-4C3C-BF1D-B2D91BD85BCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Wind" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Wind speed and wind direction calculation from u10 and v10 vector fields</t>
   </si>
@@ -68,7 +68,16 @@
     <t>vel = (u10**2 + v10**2)**0.5</t>
   </si>
   <si>
-    <t>dir = (math.atan2(v10, u10) * 180 / math.pi) % 360</t>
+    <t>dir = (180 + math.atan2(u10, v10) * 180 / math.pi) % 360</t>
+  </si>
+  <si>
+    <t>QGIS</t>
+  </si>
+  <si>
+    <t>WindVel = ("u10_mean"^2 + "v10_stat_v10_mean"^2)^0.5</t>
+  </si>
+  <si>
+    <t>WindDir = (180 + atan2("u10_mean", "v10_stat_v10_mean") * 180 / pi()) % 360</t>
   </si>
 </sst>
 </file>
@@ -454,11 +463,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51C11F4-B029-46A6-B1B9-D3E8BF3A8046}">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:D15"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="8.86328125" style="1"/>
+    <col min="3" max="3" width="15.9296875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.6">
@@ -471,7 +482,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>-5</v>
+        <v>-0.35</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -482,7 +493,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>1.18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -494,7 +505,7 @@
       </c>
       <c r="C5" s="1">
         <f>(C3^2+C4^2)^0.5</f>
-        <v>9.4339811320566032</v>
+        <v>1.2308127396155761</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.6">
@@ -502,8 +513,8 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <f>MOD(ATAN2(C3,C4)*180/PI(),360)</f>
-        <v>122.0053832080835</v>
+        <f>MOD(180 + ATAN2(C3,C4)*180/PI(),360)</f>
+        <v>286.52089218900352</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.6">
@@ -524,6 +535,21 @@
     <row r="11" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B11" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
